--- a/data/trans_dic/IQ23_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que duermen las horas recomendadas en función de su edad</t>
+          <t>Menores que duermen las horas recomendadas en función de su edad (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,89; 79,72</t>
+          <t>64,82; 80,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,07; 76,28</t>
+          <t>61,03; 76,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,98; 79,83</t>
+          <t>61,52; 80,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,35; 79,32</t>
+          <t>48,47; 78,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,31; 72,3</t>
+          <t>56,15; 73,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,53; 77,02</t>
+          <t>59,69; 76,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,33; 72,59</t>
+          <t>53,41; 72,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,63; 73,5</t>
+          <t>51,95; 72,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63,44; 75,14</t>
+          <t>64,08; 75,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,56; 74,56</t>
+          <t>62,39; 74,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60,38; 74,07</t>
+          <t>59,9; 73,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,0; 73,36</t>
+          <t>54,38; 72,86</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,74; 76,14</t>
+          <t>69,4; 76,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,51; 74,9</t>
+          <t>67,82; 75,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,13; 74,07</t>
+          <t>67,31; 74,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67,63; 76,62</t>
+          <t>67,42; 77,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,01; 78,92</t>
+          <t>72,54; 78,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,97; 75,52</t>
+          <t>68,67; 75,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,24; 70,9</t>
+          <t>63,93; 70,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>64,69; 72,77</t>
+          <t>64,18; 72,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72,19; 76,75</t>
+          <t>72,27; 76,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,7; 74,24</t>
+          <t>69,72; 74,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66,55; 71,4</t>
+          <t>66,83; 71,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,93; 73,32</t>
+          <t>66,86; 72,92</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69,79; 80,48</t>
+          <t>70,3; 81,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,51; 79,53</t>
+          <t>67,33; 78,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,17; 68,3</t>
+          <t>55,36; 68,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,5; 79,21</t>
+          <t>67,05; 78,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,03; 78,52</t>
+          <t>67,16; 78,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,71; 76,3</t>
+          <t>65,41; 76,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,42; 72,52</t>
+          <t>61,48; 72,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,73; 80,76</t>
+          <t>69,59; 80,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69,81; 78,21</t>
+          <t>70,88; 78,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,66; 76,27</t>
+          <t>68,57; 76,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60,32; 68,54</t>
+          <t>60,53; 68,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,46; 78,5</t>
+          <t>69,87; 78,03</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,17; 76,38</t>
+          <t>70,72; 76,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,15; 74,47</t>
+          <t>69,04; 74,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,99; 71,6</t>
+          <t>65,99; 71,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68,29; 75,46</t>
+          <t>67,86; 75,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,36; 76,59</t>
+          <t>71,38; 76,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,87; 74,01</t>
+          <t>68,61; 74,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,18; 69,86</t>
+          <t>64,22; 69,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66,64; 73,23</t>
+          <t>66,24; 72,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,04; 75,91</t>
+          <t>71,78; 75,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,57; 73,57</t>
+          <t>69,7; 73,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65,75; 69,67</t>
+          <t>65,38; 69,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,1; 72,9</t>
+          <t>67,87; 73,03</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que duermen las horas recomendadas en función de su edad (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>65400</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>63826</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42630</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34836</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59010</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43023</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>39236</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>121395</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>122836</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>85653</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>74072</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>58111; 71879</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56374; 71088</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36531; 47837</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25837; 41845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>48002; 62533</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>51452; 65656</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>36237; 49100</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>32209; 44881</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>112231; 132457</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>111409; 132409</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>76207; 94006</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>62706; 84014</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>301024</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>324323</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>332469</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>326499</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>361778</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>357298</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>326411</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>352960</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>662802</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>681620</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>658880</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>679459</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>286694; 314408</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>306248; 339943</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>316306; 349905</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>308261; 356542</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>345514; 375499</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>339554; 372594</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>309484; 341481</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>330276; 373329</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>642759; 683501</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>659497; 702580</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>637530; 681878</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>649775; 708687</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>130748</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>122802</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>105495</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>108151</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>114594</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>121006</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>124842</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>138177</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>245342</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>243808</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>230337</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>246327</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>121189; 139651</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>111792; 131047</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>94068; 115755</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99060; 116267</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>105411; 122647</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>111781; 131159</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>114552; 134880</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>127587; 147843</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>233428; 258776</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>231018; 257533</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>215628; 245217</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>231334; 258359</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>497172</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>510951</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>480594</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>469486</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>532367</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>537314</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>530373</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1029539</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1048265</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>974870</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>999859</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>477467; 514381</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>490168; 529356</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>461446; 500446</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>446675; 496221</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>513045; 549094</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>515624; 558156</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>474082; 515200</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>503401; 552053</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1000496; 1054812</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1018699; 1075360</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>939878; 999255</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>962550; 1035668</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IQ23_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,82; 80,18</t>
+          <t>65,12; 80,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,03; 76,96</t>
+          <t>61,04; 76,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,52; 80,56</t>
+          <t>61,79; 80,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,47; 78,51</t>
+          <t>50,07; 79,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,15; 73,15</t>
+          <t>57,79; 73,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,69; 76,17</t>
+          <t>59,63; 76,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,41; 72,37</t>
+          <t>53,68; 73,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,95; 72,38</t>
+          <t>50,94; 73,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64,08; 75,63</t>
+          <t>63,91; 74,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,39; 74,15</t>
+          <t>63,05; 74,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59,9; 73,89</t>
+          <t>60,09; 74,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,38; 72,86</t>
+          <t>54,82; 73,56</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>69,4; 76,11</t>
+          <t>68,99; 75,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,82; 75,29</t>
+          <t>68,49; 75,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,31; 74,46</t>
+          <t>67,3; 73,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67,42; 77,98</t>
+          <t>67,49; 77,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,54; 78,84</t>
+          <t>72,46; 78,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,67; 75,36</t>
+          <t>68,98; 75,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,93; 70,54</t>
+          <t>63,53; 70,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>64,18; 72,54</t>
+          <t>64,29; 72,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72,27; 76,85</t>
+          <t>72,26; 76,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,72; 74,27</t>
+          <t>69,64; 74,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66,83; 71,47</t>
+          <t>66,68; 71,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,86; 72,92</t>
+          <t>66,76; 73,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,3; 81,01</t>
+          <t>70,11; 80,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,33; 78,93</t>
+          <t>67,81; 79,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,36; 68,12</t>
+          <t>56,07; 68,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,05; 78,69</t>
+          <t>67,01; 78,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,16; 78,14</t>
+          <t>67,01; 78,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,41; 76,75</t>
+          <t>65,27; 76,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,48; 72,39</t>
+          <t>61,09; 72,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,59; 80,63</t>
+          <t>69,42; 80,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,88; 78,57</t>
+          <t>70,26; 77,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,57; 76,44</t>
+          <t>68,21; 76,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60,53; 68,83</t>
+          <t>60,78; 69,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69,87; 78,03</t>
+          <t>70,16; 78,04</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,72; 76,19</t>
+          <t>70,92; 76,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,04; 74,56</t>
+          <t>69,23; 74,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,99; 71,57</t>
+          <t>65,55; 71,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67,86; 75,39</t>
+          <t>67,96; 75,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,38; 76,4</t>
+          <t>71,33; 76,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,61; 74,27</t>
+          <t>68,85; 74,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,22; 69,79</t>
+          <t>64,03; 69,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66,24; 72,64</t>
+          <t>66,35; 72,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,78; 75,67</t>
+          <t>72,03; 75,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,7; 73,58</t>
+          <t>69,61; 73,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65,38; 69,51</t>
+          <t>65,79; 69,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,87; 73,03</t>
+          <t>68,07; 72,89</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>58111; 71879</t>
+          <t>58377; 72132</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56374; 71088</t>
+          <t>56387; 71000</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36531; 47837</t>
+          <t>36693; 47524</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25837; 41845</t>
+          <t>26686; 42335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>48002; 62533</t>
+          <t>49401; 62720</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51452; 65656</t>
+          <t>51395; 66081</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36237; 49100</t>
+          <t>36423; 49808</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32209; 44881</t>
+          <t>31586; 45320</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>112231; 132457</t>
+          <t>111929; 131314</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>111409; 132409</t>
+          <t>112576; 132923</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76207; 94006</t>
+          <t>76457; 94548</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62706; 84014</t>
+          <t>63211; 84820</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>286694; 314408</t>
+          <t>285001; 313706</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>306248; 339943</t>
+          <t>309275; 340757</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>316306; 349905</t>
+          <t>316268; 346305</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>308261; 356542</t>
+          <t>308559; 355661</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>345514; 375499</t>
+          <t>345117; 374526</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>339554; 372594</t>
+          <t>341092; 373359</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>309484; 341481</t>
+          <t>307511; 342376</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>330276; 373329</t>
+          <t>330843; 372823</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>642759; 683501</t>
+          <t>642665; 682975</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>659497; 702580</t>
+          <t>658789; 706023</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>637530; 681878</t>
+          <t>636104; 682300</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>649775; 708687</t>
+          <t>648742; 713674</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>121189; 139651</t>
+          <t>120866; 139157</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>111792; 131047</t>
+          <t>112586; 132310</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94068; 115755</t>
+          <t>95286; 116252</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99060; 116267</t>
+          <t>99006; 115745</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>105411; 122647</t>
+          <t>105173; 122785</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>111781; 131159</t>
+          <t>111540; 130618</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>114552; 134880</t>
+          <t>113822; 135137</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>127587; 147843</t>
+          <t>127288; 147970</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>233428; 258776</t>
+          <t>231403; 256873</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>231018; 257533</t>
+          <t>229808; 256882</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>215628; 245217</t>
+          <t>216512; 246111</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>231334; 258359</t>
+          <t>232299; 258396</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>477467; 514381</t>
+          <t>478826; 515681</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>490168; 529356</t>
+          <t>491483; 531483</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>461446; 500446</t>
+          <t>458336; 497620</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>446675; 496221</t>
+          <t>447342; 496429</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>513045; 549094</t>
+          <t>512705; 550480</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>515624; 558156</t>
+          <t>517416; 557587</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>474082; 515200</t>
+          <t>472693; 515355</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>503401; 552053</t>
+          <t>504217; 554632</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1000496; 1054812</t>
+          <t>1004034; 1054463</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1018699; 1075360</t>
+          <t>1017388; 1076158</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>939878; 999255</t>
+          <t>945678; 1002204</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>962550; 1035668</t>
+          <t>965413; 1033705</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IQ23_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>65,5%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>68,46%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63,41%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>64,02%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>72,95%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>69,1%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>71,79%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>65,36%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>65,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,41%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,3%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,12; 80,46</t>
+          <t>56,31; 72,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,04; 76,87</t>
+          <t>60,53; 77,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,79; 80,04</t>
+          <t>53,33; 72,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,07; 79,43</t>
+          <t>52,2; 74,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,79; 73,37</t>
+          <t>64,89; 79,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,63; 76,67</t>
+          <t>61,07; 76,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,68; 73,41</t>
+          <t>61,98; 79,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,94; 73,09</t>
+          <t>51,69; 75,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63,91; 74,98</t>
+          <t>63,44; 75,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63,05; 74,44</t>
+          <t>62,56; 74,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60,09; 74,31</t>
+          <t>60,38; 74,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,82; 73,56</t>
+          <t>56,32; 72,36</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75,96%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>72,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>69,86%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>72,87%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>71,83%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>70,75%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71,41%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>75,96%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>67,43%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,99; 75,94</t>
+          <t>73,01; 78,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,49; 75,47</t>
+          <t>68,97; 75,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,3; 73,69</t>
+          <t>64,24; 70,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67,49; 77,79</t>
+          <t>66,03; 73,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,46; 78,63</t>
+          <t>68,74; 76,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,98; 75,51</t>
+          <t>68,51; 74,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,53; 70,73</t>
+          <t>67,13; 74,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>64,29; 72,45</t>
+          <t>67,13; 73,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72,26; 76,79</t>
+          <t>72,19; 76,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,64; 74,63</t>
+          <t>69,7; 74,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66,68; 71,52</t>
+          <t>66,55; 71,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,76; 73,44</t>
+          <t>67,48; 72,94</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70,81%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>67,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76,44%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>75,85%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>73,97%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>62,08%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67,0%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>75,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,11; 80,72</t>
+          <t>67,03; 78,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,81; 79,69</t>
+          <t>64,71; 76,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,07; 68,41</t>
+          <t>61,42; 72,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,01; 78,34</t>
+          <t>70,96; 81,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,01; 78,23</t>
+          <t>69,79; 80,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,27; 76,43</t>
+          <t>68,51; 79,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,09; 72,53</t>
+          <t>56,17; 68,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,42; 80,7</t>
+          <t>68,25; 79,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,26; 77,99</t>
+          <t>69,81; 78,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,21; 76,24</t>
+          <t>68,66; 76,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60,78; 69,08</t>
+          <t>60,32; 68,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,16; 78,04</t>
+          <t>71,29; 79,21</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74,07%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>71,5%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>66,95%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>70,97%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>73,64%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>71,97%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>68,73%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>71,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>74,07%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>71,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,95%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,92; 76,38</t>
+          <t>71,36; 76,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,23; 74,86</t>
+          <t>68,87; 74,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,55; 71,16</t>
+          <t>64,18; 69,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67,96; 75,42</t>
+          <t>67,79; 74,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,33; 76,59</t>
+          <t>71,17; 76,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,85; 74,19</t>
+          <t>69,15; 74,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,03; 69,81</t>
+          <t>65,99; 71,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66,35; 72,98</t>
+          <t>68,07; 73,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,03; 75,65</t>
+          <t>72,04; 75,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,61; 73,64</t>
+          <t>69,57; 73,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65,79; 69,72</t>
+          <t>65,75; 69,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,07; 72,89</t>
+          <t>68,83; 73,12</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59010</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43023</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36317</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>65400</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>63826</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>42630</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34836</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>55996</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>59010</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43023</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>29511</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74072</t>
+          <t>65828</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>58377; 72132</t>
+          <t>48134; 61808</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56387; 71000</t>
+          <t>52176; 66387</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36693; 47524</t>
+          <t>36184; 49250</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26686; 42335</t>
+          <t>29612; 42217</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>49401; 62720</t>
+          <t>58168; 71469</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51395; 66081</t>
+          <t>56414; 70459</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36423; 49808</t>
+          <t>36805; 47404</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31586; 45320</t>
+          <t>23593; 34636</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>111929; 131314</t>
+          <t>111100; 131592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112576; 132923</t>
+          <t>111705; 133133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76457; 94548</t>
+          <t>76827; 94232</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63211; 84820</t>
+          <t>57663; 74079</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>466</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>426</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>428</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>361778</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>357298</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>326411</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>330978</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>301024</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>324323</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>332469</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>326499</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>361778</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>357298</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>326411</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>352960</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>679459</t>
+          <t>634725</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>285001; 313706</t>
+          <t>347730; 375904</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>309275; 340757</t>
+          <t>341005; 373386</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>316268; 346305</t>
+          <t>310964; 343219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>308559; 355661</t>
+          <t>312822; 350235</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>345117; 374526</t>
+          <t>283963; 314547</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>341092; 373359</t>
+          <t>309324; 338190</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>307511; 342376</t>
+          <t>315482; 348110</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>330843; 372823</t>
+          <t>288142; 317224</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>642665; 682975</t>
+          <t>642103; 682612</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>658789; 706023</t>
+          <t>659322; 702276</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>636104; 682300</t>
+          <t>634904; 681137</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>648742; 713674</t>
+          <t>609311; 658677</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>162</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>114594</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>121006</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>124842</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>128737</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>130748</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>122802</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>105495</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108151</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>114594</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>121006</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>124842</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>138177</t>
+          <t>109476</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>246327</t>
+          <t>238212</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>120866; 139157</t>
+          <t>105205; 123238</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>112586; 132310</t>
+          <t>110580; 130396</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95286; 116252</t>
+          <t>114435; 135124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99006; 115745</t>
+          <t>119510; 137462</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>105173; 122785</t>
+          <t>120303; 138733</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>111540; 130618</t>
+          <t>113749; 132042</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>113822; 135137</t>
+          <t>95457; 116060</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>127288; 147970</t>
+          <t>101033; 118239</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>231403; 256873</t>
+          <t>229909; 257592</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>229808; 256882</t>
+          <t>231315; 256956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>216512; 246111</t>
+          <t>214891; 244183</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>232299; 258396</t>
+          <t>225601; 250661</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>716</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>630</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>532367</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>537314</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>496031</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>497172</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>510951</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>480594</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>469486</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>532367</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>537314</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>494276</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>530373</t>
+          <t>442734</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>999859</t>
+          <t>938765</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>478826; 515681</t>
+          <t>512900; 550520</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>491483; 531483</t>
+          <t>517554; 556219</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>458336; 497620</t>
+          <t>473777; 515717</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>447342; 496429</t>
+          <t>473783; 518880</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>512705; 550480</t>
+          <t>480522; 515664</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>517416; 557587</t>
+          <t>490900; 528676</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>472693; 515355</t>
+          <t>461458; 500683</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>504217; 554632</t>
+          <t>423999; 460413</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1004034; 1054463</t>
+          <t>1004191; 1058095</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1017388; 1076158</t>
+          <t>1016741; 1075236</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>945678; 1002204</t>
+          <t>945109; 1001563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>965413; 1033705</t>
+          <t>909859; 966511</t>
         </is>
       </c>
     </row>
